--- a/Apostas_Diarias/Apostas_20260427.xlsx
+++ b/Apostas_Diarias/Apostas_20260427.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_2B590F4F9566CA512D42C9F0508D70334921E09D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{177222E6-999C-44D1-9708-183FF3914113}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_2B590F4F95D64B526522CDF05035883157A5F405" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82B9E23B-6AFA-43DF-8D5A-0EC90B9D1808}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Data</t>
   </si>
@@ -74,36 +74,18 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>07:00:00</t>
-  </si>
-  <si>
-    <t>UKRAINE 1</t>
-  </si>
-  <si>
-    <t>FC Epicentr Dunaivtsi x Oleksandria</t>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>SERBIA 1</t>
+  </si>
+  <si>
+    <t>FK Radnicki 1923 x FK Spartak</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
-    <t>ROMANIA 1</t>
-  </si>
-  <si>
-    <t>FC Metaloglobus Bucuresti x Unirea Slobozia</t>
-  </si>
-  <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>SERBIA 1</t>
-  </si>
-  <si>
-    <t>FK Radnicki 1923 x FK Spartak</t>
-  </si>
-  <si>
     <t>13:30:00</t>
   </si>
   <si>
@@ -111,42 +93,6 @@
   </si>
   <si>
     <t>Cagliari x Atalanta</t>
-  </si>
-  <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>TURKEY 1</t>
-  </si>
-  <si>
-    <t>Konyaspor x Trabzonspor</t>
-  </si>
-  <si>
-    <t>14:50:00</t>
-  </si>
-  <si>
-    <t>SAUDI ARABIA 1</t>
-  </si>
-  <si>
-    <t>Al-Jndal x Al Orubah</t>
-  </si>
-  <si>
-    <t>15:45:00</t>
-  </si>
-  <si>
-    <t>FRANCE 2</t>
-  </si>
-  <si>
-    <t>Boulogne x Dunkerque</t>
-  </si>
-  <si>
-    <t>18:45:00</t>
-  </si>
-  <si>
-    <t>ARGENTINA 1</t>
-  </si>
-  <si>
-    <t>Velez Sarsfield x Union Santa Fe</t>
   </si>
   <si>
     <t>P2</t>
@@ -498,14 +444,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -569,10 +514,10 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>500</v>
@@ -583,7 +528,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>38.958333333333336</v>
+        <v>24.605263157894736</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -609,21 +554,21 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J10" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J4" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K10" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>51.944444444444443</v>
+        <f t="shared" ref="K3:K4" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>58.4375</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -634,25 +579,25 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>500</v>
@@ -663,249 +608,9 @@
       </c>
       <c r="K4">
         <f t="shared" si="1"/>
-        <v>9.5408163265306118</v>
+        <v>63.175675675675684</v>
       </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="1"/>
-        <v>58.4375</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>12.5</v>
-      </c>
-      <c r="H6">
-        <v>12.5</v>
-      </c>
-      <c r="I6">
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="1"/>
-        <v>40.652173913043484</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>9.6</v>
-      </c>
-      <c r="H7">
-        <v>9.6</v>
-      </c>
-      <c r="I7">
-        <v>500</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="1"/>
-        <v>54.360465116279073</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>10.5</v>
-      </c>
-      <c r="H8">
-        <v>10.5</v>
-      </c>
-      <c r="I8">
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9">
-        <v>11</v>
-      </c>
-      <c r="H9">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <v>500</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="1"/>
-        <v>46.75</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10">
-        <v>8.4</v>
-      </c>
-      <c r="H10">
-        <v>8.4</v>
-      </c>
-      <c r="I10">
-        <v>500</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="1"/>
-        <v>63.175675675675684</v>
-      </c>
-      <c r="L10">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260427.xlsx
+++ b/Apostas_Diarias/Apostas_20260427.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_2B590F4F95D64B526522CDF05035883157A5F405" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82B9E23B-6AFA-43DF-8D5A-0EC90B9D1808}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F95264665A9C0D8F05096E8377F8FF512" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB85FFC6-E8EC-4714-A364-228684B82336}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Data</t>
   </si>
@@ -74,13 +74,13 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>SERBIA 1</t>
-  </si>
-  <si>
-    <t>FK Radnicki 1923 x FK Spartak</t>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>ROMANIA 1</t>
+  </si>
+  <si>
+    <t>FC Metaloglobus Bucuresti x Unirea Slobozia</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
@@ -95,16 +95,13 @@
     <t>Cagliari x Atalanta</t>
   </si>
   <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
-    <t>SPAIN 2</t>
-  </si>
-  <si>
-    <t>Cadiz x Las Palmas</t>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>FRANCE 2</t>
+  </si>
+  <si>
+    <t>Boulogne x Dunkerque</t>
   </si>
 </sst>
 </file>
@@ -449,8 +446,9 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="33" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -493,6 +491,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -514,12 +515,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <f>G2</f>
+        <v>10</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -528,7 +531,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>24.605263157894736</v>
+        <v>51.944444444444443</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -557,17 +560,19 @@
         <v>9</v>
       </c>
       <c r="H3">
+        <f t="shared" ref="H3:H4" si="0">G3</f>
         <v>9</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I4" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J4" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J4" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K4" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <f t="shared" ref="K3:K4" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
         <v>58.4375</v>
       </c>
       <c r="L3">
@@ -579,36 +584,38 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
-        <v>63.175675675675684</v>
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
       </c>
       <c r="L4">
         <v>1</v>

--- a/Apostas_Diarias/Apostas_20260427.xlsx
+++ b/Apostas_Diarias/Apostas_20260427.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F95264665A9C0D8F05096E8377F8FF512" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB85FFC6-E8EC-4714-A364-228684B82336}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_2B590F4F95D64B526522CDF05035883157A5F405" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82B9E23B-6AFA-43DF-8D5A-0EC90B9D1808}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Data</t>
   </si>
@@ -74,13 +74,13 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
-    <t>ROMANIA 1</t>
-  </si>
-  <si>
-    <t>FC Metaloglobus Bucuresti x Unirea Slobozia</t>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>SERBIA 1</t>
+  </si>
+  <si>
+    <t>FK Radnicki 1923 x FK Spartak</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
@@ -95,13 +95,16 @@
     <t>Cagliari x Atalanta</t>
   </si>
   <si>
-    <t>15:45:00</t>
-  </si>
-  <si>
-    <t>FRANCE 2</t>
-  </si>
-  <si>
-    <t>Boulogne x Dunkerque</t>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>SPAIN 2</t>
+  </si>
+  <si>
+    <t>Cadiz x Las Palmas</t>
   </si>
 </sst>
 </file>
@@ -446,9 +449,8 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -491,9 +493,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -515,14 +514,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -531,7 +528,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>51.944444444444443</v>
+        <v>24.605263157894736</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -560,19 +557,17 @@
         <v>9</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H4" si="0">G3</f>
         <v>9</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I4" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J4" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J4" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K4" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <f t="shared" ref="K3:K4" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
         <v>58.4375</v>
       </c>
       <c r="L3">
@@ -584,38 +579,36 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="H4">
+        <v>8.4</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I4">
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>49.210526315789473</v>
+        <v>63.175675675675684</v>
       </c>
       <c r="L4">
         <v>1</v>
